--- a/SIWES_IT_Placement_Tracker_2027.xlsx
+++ b/SIWES_IT_Placement_Tracker_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\My Datasets (Projects)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB1B3188-CEF8-4B8B-B443-D665D5CA2056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD9C93A-2C59-4BE4-8AF6-1C2AEE9CD65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -152,9 +152,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="248">
   <si>
-    <t>Mercy's SIWES / IT Placement Tracker – 2027</t>
-  </si>
-  <si>
     <t>Research snapshot: 30 October 2026. 'Not confirmed' means no reliable public confirmation found; verify directly before making relocation or eligibility decisions.</t>
   </si>
   <si>
@@ -894,6 +891,9 @@
   </si>
   <si>
     <t>On Hold</t>
+  </si>
+  <si>
+    <t>SIWES / IT Placement Tracker – 2027</t>
   </si>
 </sst>
 </file>
@@ -917,18 +917,21 @@
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Display"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF555555"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -942,10 +945,12 @@
       <sz val="11"/>
       <color rgb="FF17365D"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1089,6 +1094,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1106,17 +1118,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2149,117 +2154,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+    </row>
+    <row r="2" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-    </row>
-    <row r="2" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+    </row>
+    <row r="4" spans="1:22" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-    </row>
-    <row r="4" spans="1:22" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="B4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="C4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="D4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="E4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="F4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="G4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="H4" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="I4" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="J4" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="K4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="37" t="s">
+      <c r="L4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="37" t="s">
+      <c r="M4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="N4" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="O4" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="37" t="s">
+      <c r="P4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="37" t="s">
+      <c r="Q4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="37" t="s">
+      <c r="R4" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="R4" s="37" t="s">
+      <c r="S4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="S4" s="37" t="s">
+      <c r="T4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2267,67 +2272,67 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="H5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="10" t="s">
+      <c r="P5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="R5" s="3">
         <v>9</v>
       </c>
       <c r="S5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2335,67 +2340,67 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="10" t="s">
+      <c r="P6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="Q6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R6" s="3">
         <v>9</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2403,67 +2408,67 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="10" t="s">
+      <c r="P7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="Q7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R7" s="3">
         <v>8</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2471,67 +2476,67 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" s="10" t="s">
+      <c r="P8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="Q8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R8" s="3">
         <v>8</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2539,67 +2544,67 @@
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="10" t="s">
+      <c r="P9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="Q9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R9" s="3">
         <v>8</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2607,67 +2612,67 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="N10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="25" t="s">
+      <c r="P10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="Q10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R10" s="3">
         <v>8</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2675,67 +2680,67 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" s="10" t="s">
+      <c r="P11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="Q11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R11" s="3">
         <v>7</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2743,67 +2748,67 @@
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="P12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R12" s="3">
         <v>7</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2811,67 +2816,67 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="I13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="M13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O13" s="25" t="s">
+      <c r="P13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="P13" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="Q13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R13" s="3">
         <v>7</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2879,67 +2884,67 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" s="10" t="s">
+      <c r="P14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="Q14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R14" s="3">
         <v>7</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -2947,67 +2952,67 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O15" s="10" t="s">
+      <c r="P15" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="Q15" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R15" s="3">
         <v>6</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="76" customHeight="1" x14ac:dyDescent="0.35">
@@ -3015,67 +3020,67 @@
         <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O16" s="25" t="s">
+      <c r="P16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="Q16" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R16" s="3">
         <v>4</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -3156,139 +3161,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+    </row>
+    <row r="2" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-    </row>
-    <row r="2" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+    </row>
+    <row r="4" spans="1:27" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-    </row>
-    <row r="4" spans="1:27" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="B4" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="C4" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="D4" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="G4" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="H4" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="J4" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="K4" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="L4" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="M4" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="N4" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="O4" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="P4" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="P4" s="33" t="s">
+      <c r="Q4" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="Q4" s="33" t="s">
+      <c r="R4" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="R4" s="33" t="s">
+      <c r="S4" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="S4" s="33" t="s">
+      <c r="T4" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="T4" s="33" t="s">
+      <c r="U4" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="W4" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="W4" s="9" t="s">
+      <c r="X4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="X4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y4" s="9" t="s">
+      <c r="Z4" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AA4" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="11"/>
@@ -3306,34 +3311,34 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R5" s="12"/>
       <c r="S5" s="11"/>
       <c r="T5" s="11"/>
       <c r="U5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z5" s="12"/>
       <c r="AA5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="11"/>
@@ -3351,34 +3356,34 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R6" s="12"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
       <c r="U6" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V6" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z6" s="12"/>
       <c r="AA6" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="11"/>
@@ -3396,34 +3401,34 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R7" s="12"/>
       <c r="S7" s="11"/>
       <c r="T7" s="11"/>
       <c r="U7" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z7" s="12"/>
       <c r="AA7" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="11"/>
@@ -3441,34 +3446,34 @@
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R8" s="12"/>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
       <c r="U8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V8" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z8" s="12"/>
       <c r="AA8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="11"/>
@@ -3486,34 +3491,34 @@
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R9" s="12"/>
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
       <c r="U9" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z9" s="12"/>
       <c r="AA9" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="11"/>
@@ -3531,34 +3536,34 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R10" s="12"/>
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
       <c r="U10" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V10" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z10" s="12"/>
       <c r="AA10" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="11"/>
@@ -3576,34 +3581,34 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R11" s="12"/>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V11" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X11" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z11" s="12"/>
       <c r="AA11" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="11"/>
@@ -3621,34 +3626,34 @@
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R12" s="12"/>
       <c r="S12" s="11"/>
       <c r="T12" s="11"/>
       <c r="U12" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z12" s="12"/>
       <c r="AA12" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="11"/>
@@ -3666,34 +3671,34 @@
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R13" s="12"/>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z13" s="12"/>
       <c r="AA13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="11"/>
@@ -3711,34 +3716,34 @@
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R14" s="12"/>
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
       <c r="U14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z14" s="12"/>
       <c r="AA14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="11"/>
@@ -3756,34 +3761,34 @@
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R15" s="12"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
       <c r="U15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z15" s="12"/>
       <c r="AA15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="11"/>
@@ -3801,29 +3806,29 @@
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V16" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z16" s="12"/>
       <c r="AA16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
@@ -3848,23 +3853,23 @@
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V17" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y17" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z17" s="12"/>
       <c r="AA17" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -3889,23 +3894,23 @@
       <c r="S18" s="11"/>
       <c r="T18" s="11"/>
       <c r="U18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V18" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z18" s="12"/>
       <c r="AA18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
@@ -3930,23 +3935,23 @@
       <c r="S19" s="11"/>
       <c r="T19" s="11"/>
       <c r="U19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V19" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z19" s="12"/>
       <c r="AA19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
@@ -3971,23 +3976,23 @@
       <c r="S20" s="11"/>
       <c r="T20" s="11"/>
       <c r="U20" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V20" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X20" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y20" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z20" s="12"/>
       <c r="AA20" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.35">
@@ -4012,23 +4017,23 @@
       <c r="S21" s="11"/>
       <c r="T21" s="11"/>
       <c r="U21" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W21" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z21" s="12"/>
       <c r="AA21" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.35">
@@ -4053,23 +4058,23 @@
       <c r="S22" s="11"/>
       <c r="T22" s="11"/>
       <c r="U22" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V22" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z22" s="12"/>
       <c r="AA22" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.35">
@@ -4094,23 +4099,23 @@
       <c r="S23" s="11"/>
       <c r="T23" s="11"/>
       <c r="U23" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V23" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z23" s="12"/>
       <c r="AA23" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">
@@ -4135,23 +4140,23 @@
       <c r="S24" s="11"/>
       <c r="T24" s="11"/>
       <c r="U24" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z24" s="12"/>
       <c r="AA24" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.35">
@@ -4176,23 +4181,23 @@
       <c r="S25" s="11"/>
       <c r="T25" s="11"/>
       <c r="U25" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V25" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z25" s="12"/>
       <c r="AA25" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.35">
@@ -4217,23 +4222,23 @@
       <c r="S26" s="11"/>
       <c r="T26" s="11"/>
       <c r="U26" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V26" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z26" s="12"/>
       <c r="AA26" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">
@@ -4258,23 +4263,23 @@
       <c r="S27" s="11"/>
       <c r="T27" s="11"/>
       <c r="U27" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V27" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y27" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z27" s="12"/>
       <c r="AA27" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.35">
@@ -4299,23 +4304,23 @@
       <c r="S28" s="11"/>
       <c r="T28" s="11"/>
       <c r="U28" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V28" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y28" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z28" s="12"/>
       <c r="AA28" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.35">
@@ -4340,23 +4345,23 @@
       <c r="S29" s="11"/>
       <c r="T29" s="11"/>
       <c r="U29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.35">
@@ -4381,23 +4386,23 @@
       <c r="S30" s="11"/>
       <c r="T30" s="11"/>
       <c r="U30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V30" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z30" s="12"/>
       <c r="AA30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.35">
@@ -4422,23 +4427,23 @@
       <c r="S31" s="11"/>
       <c r="T31" s="11"/>
       <c r="U31" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V31" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y31" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z31" s="12"/>
       <c r="AA31" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.35">
@@ -4463,23 +4468,23 @@
       <c r="S32" s="11"/>
       <c r="T32" s="11"/>
       <c r="U32" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V32" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z32" s="12"/>
       <c r="AA32" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.35">
@@ -4504,23 +4509,23 @@
       <c r="S33" s="11"/>
       <c r="T33" s="11"/>
       <c r="U33" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V33" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W33" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y33" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z33" s="12"/>
       <c r="AA33" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.35">
@@ -4545,23 +4550,23 @@
       <c r="S34" s="11"/>
       <c r="T34" s="11"/>
       <c r="U34" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V34" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y34" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z34" s="12"/>
       <c r="AA34" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.35">
@@ -4586,23 +4591,23 @@
       <c r="S35" s="11"/>
       <c r="T35" s="11"/>
       <c r="U35" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V35" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W35" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X35" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y35" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z35" s="12"/>
       <c r="AA35" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.35">
@@ -4627,23 +4632,23 @@
       <c r="S36" s="11"/>
       <c r="T36" s="11"/>
       <c r="U36" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V36" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W36" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X36" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y36" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z36" s="12"/>
       <c r="AA36" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.35">
@@ -4668,23 +4673,23 @@
       <c r="S37" s="11"/>
       <c r="T37" s="11"/>
       <c r="U37" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V37" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W37" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X37" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y37" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z37" s="12"/>
       <c r="AA37" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.35">
@@ -4709,23 +4714,23 @@
       <c r="S38" s="11"/>
       <c r="T38" s="11"/>
       <c r="U38" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V38" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W38" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X38" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y38" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z38" s="12"/>
       <c r="AA38" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.35">
@@ -4750,23 +4755,23 @@
       <c r="S39" s="11"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V39" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W39" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X39" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y39" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z39" s="12"/>
       <c r="AA39" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.35">
@@ -4791,23 +4796,23 @@
       <c r="S40" s="11"/>
       <c r="T40" s="11"/>
       <c r="U40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V40" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z40" s="12"/>
       <c r="AA40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.35">
@@ -4832,23 +4837,23 @@
       <c r="S41" s="11"/>
       <c r="T41" s="11"/>
       <c r="U41" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V41" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W41" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X41" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y41" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="12"/>
       <c r="AA41" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.35">
@@ -4873,23 +4878,23 @@
       <c r="S42" s="11"/>
       <c r="T42" s="11"/>
       <c r="U42" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V42" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W42" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X42" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y42" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z42" s="12"/>
       <c r="AA42" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.35">
@@ -4914,23 +4919,23 @@
       <c r="S43" s="11"/>
       <c r="T43" s="11"/>
       <c r="U43" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V43" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W43" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X43" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y43" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z43" s="12"/>
       <c r="AA43" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.35">
@@ -4955,23 +4960,23 @@
       <c r="S44" s="11"/>
       <c r="T44" s="11"/>
       <c r="U44" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V44" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W44" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X44" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y44" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z44" s="12"/>
       <c r="AA44" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.35">
@@ -4996,23 +5001,23 @@
       <c r="S45" s="11"/>
       <c r="T45" s="11"/>
       <c r="U45" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V45" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W45" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X45" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y45" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z45" s="12"/>
       <c r="AA45" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.35">
@@ -5037,23 +5042,23 @@
       <c r="S46" s="11"/>
       <c r="T46" s="11"/>
       <c r="U46" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V46" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W46" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X46" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y46" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z46" s="12"/>
       <c r="AA46" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.35">
@@ -5078,23 +5083,23 @@
       <c r="S47" s="11"/>
       <c r="T47" s="11"/>
       <c r="U47" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V47" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W47" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X47" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y47" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z47" s="12"/>
       <c r="AA47" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.35">
@@ -5119,23 +5124,23 @@
       <c r="S48" s="11"/>
       <c r="T48" s="11"/>
       <c r="U48" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V48" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W48" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X48" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y48" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z48" s="12"/>
       <c r="AA48" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.35">
@@ -5160,23 +5165,23 @@
       <c r="S49" s="11"/>
       <c r="T49" s="11"/>
       <c r="U49" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V49" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W49" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X49" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y49" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z49" s="12"/>
       <c r="AA49" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.35">
@@ -5201,23 +5206,23 @@
       <c r="S50" s="11"/>
       <c r="T50" s="11"/>
       <c r="U50" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V50" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W50" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X50" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y50" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z50" s="12"/>
       <c r="AA50" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.35">
@@ -5242,23 +5247,23 @@
       <c r="S51" s="11"/>
       <c r="T51" s="11"/>
       <c r="U51" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V51" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W51" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X51" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y51" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z51" s="12"/>
       <c r="AA51" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.35">
@@ -5283,23 +5288,23 @@
       <c r="S52" s="11"/>
       <c r="T52" s="11"/>
       <c r="U52" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V52" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W52" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X52" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y52" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z52" s="12"/>
       <c r="AA52" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.35">
@@ -5324,23 +5329,23 @@
       <c r="S53" s="11"/>
       <c r="T53" s="11"/>
       <c r="U53" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V53" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W53" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X53" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y53" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z53" s="12"/>
       <c r="AA53" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.35">
@@ -5365,23 +5370,23 @@
       <c r="S54" s="11"/>
       <c r="T54" s="11"/>
       <c r="U54" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V54" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W54" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X54" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y54" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z54" s="12"/>
       <c r="AA54" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.35">
@@ -5406,23 +5411,23 @@
       <c r="S55" s="11"/>
       <c r="T55" s="11"/>
       <c r="U55" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V55" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W55" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X55" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y55" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z55" s="12"/>
       <c r="AA55" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.35">
@@ -5447,23 +5452,23 @@
       <c r="S56" s="11"/>
       <c r="T56" s="11"/>
       <c r="U56" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V56" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W56" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X56" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y56" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z56" s="12"/>
       <c r="AA56" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.35">
@@ -5488,23 +5493,23 @@
       <c r="S57" s="11"/>
       <c r="T57" s="11"/>
       <c r="U57" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V57" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W57" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X57" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y57" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z57" s="12"/>
       <c r="AA57" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.35">
@@ -5529,23 +5534,23 @@
       <c r="S58" s="11"/>
       <c r="T58" s="11"/>
       <c r="U58" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V58" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W58" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X58" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y58" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z58" s="12"/>
       <c r="AA58" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.35">
@@ -5570,23 +5575,23 @@
       <c r="S59" s="11"/>
       <c r="T59" s="11"/>
       <c r="U59" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V59" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W59" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X59" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y59" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z59" s="12"/>
       <c r="AA59" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.35">
@@ -5611,23 +5616,23 @@
       <c r="S60" s="11"/>
       <c r="T60" s="11"/>
       <c r="U60" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V60" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W60" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X60" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y60" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z60" s="12"/>
       <c r="AA60" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.35">
@@ -5652,23 +5657,23 @@
       <c r="S61" s="11"/>
       <c r="T61" s="11"/>
       <c r="U61" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V61" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W61" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X61" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y61" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z61" s="12"/>
       <c r="AA61" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.35">
@@ -5693,23 +5698,23 @@
       <c r="S62" s="11"/>
       <c r="T62" s="11"/>
       <c r="U62" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V62" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W62" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X62" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y62" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z62" s="12"/>
       <c r="AA62" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.35">
@@ -5734,23 +5739,23 @@
       <c r="S63" s="11"/>
       <c r="T63" s="11"/>
       <c r="U63" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V63" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W63" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X63" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y63" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z63" s="12"/>
       <c r="AA63" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.35">
@@ -5775,23 +5780,23 @@
       <c r="S64" s="11"/>
       <c r="T64" s="11"/>
       <c r="U64" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V64" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W64" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X64" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y64" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z64" s="12"/>
       <c r="AA64" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.35">
@@ -5816,23 +5821,23 @@
       <c r="S65" s="11"/>
       <c r="T65" s="11"/>
       <c r="U65" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V65" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W65" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X65" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y65" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z65" s="12"/>
       <c r="AA65" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.35">
@@ -5857,23 +5862,23 @@
       <c r="S66" s="11"/>
       <c r="T66" s="11"/>
       <c r="U66" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V66" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W66" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X66" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y66" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z66" s="12"/>
       <c r="AA66" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.35">
@@ -5898,23 +5903,23 @@
       <c r="S67" s="11"/>
       <c r="T67" s="11"/>
       <c r="U67" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V67" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W67" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X67" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y67" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z67" s="12"/>
       <c r="AA67" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.35">
@@ -5939,23 +5944,23 @@
       <c r="S68" s="11"/>
       <c r="T68" s="11"/>
       <c r="U68" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V68" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W68" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X68" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y68" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z68" s="12"/>
       <c r="AA68" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.35">
@@ -5980,23 +5985,23 @@
       <c r="S69" s="11"/>
       <c r="T69" s="11"/>
       <c r="U69" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V69" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W69" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X69" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y69" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z69" s="12"/>
       <c r="AA69" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.35">
@@ -6021,23 +6026,23 @@
       <c r="S70" s="11"/>
       <c r="T70" s="11"/>
       <c r="U70" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V70" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W70" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X70" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y70" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z70" s="12"/>
       <c r="AA70" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.35">
@@ -6062,23 +6067,23 @@
       <c r="S71" s="11"/>
       <c r="T71" s="11"/>
       <c r="U71" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V71" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W71" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X71" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y71" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z71" s="12"/>
       <c r="AA71" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.35">
@@ -6103,23 +6108,23 @@
       <c r="S72" s="11"/>
       <c r="T72" s="11"/>
       <c r="U72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V72" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z72" s="12"/>
       <c r="AA72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.35">
@@ -6144,23 +6149,23 @@
       <c r="S73" s="11"/>
       <c r="T73" s="11"/>
       <c r="U73" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V73" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W73" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X73" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y73" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z73" s="12"/>
       <c r="AA73" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.35">
@@ -6185,23 +6190,23 @@
       <c r="S74" s="11"/>
       <c r="T74" s="11"/>
       <c r="U74" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V74" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W74" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X74" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y74" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z74" s="12"/>
       <c r="AA74" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.35">
@@ -6226,23 +6231,23 @@
       <c r="S75" s="11"/>
       <c r="T75" s="11"/>
       <c r="U75" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V75" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W75" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X75" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y75" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z75" s="12"/>
       <c r="AA75" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.35">
@@ -6267,23 +6272,23 @@
       <c r="S76" s="11"/>
       <c r="T76" s="11"/>
       <c r="U76" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V76" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W76" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X76" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y76" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z76" s="12"/>
       <c r="AA76" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.35">
@@ -6308,23 +6313,23 @@
       <c r="S77" s="11"/>
       <c r="T77" s="11"/>
       <c r="U77" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V77" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W77" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X77" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y77" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z77" s="12"/>
       <c r="AA77" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.35">
@@ -6349,23 +6354,23 @@
       <c r="S78" s="11"/>
       <c r="T78" s="11"/>
       <c r="U78" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V78" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W78" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X78" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y78" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z78" s="12"/>
       <c r="AA78" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.35">
@@ -6390,23 +6395,23 @@
       <c r="S79" s="11"/>
       <c r="T79" s="11"/>
       <c r="U79" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V79" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W79" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X79" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y79" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z79" s="12"/>
       <c r="AA79" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.35">
@@ -6431,23 +6436,23 @@
       <c r="S80" s="11"/>
       <c r="T80" s="11"/>
       <c r="U80" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V80" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W80" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X80" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y80" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z80" s="12"/>
       <c r="AA80" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.35">
@@ -6472,23 +6477,23 @@
       <c r="S81" s="11"/>
       <c r="T81" s="11"/>
       <c r="U81" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V81" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W81" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X81" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y81" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z81" s="12"/>
       <c r="AA81" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.35">
@@ -6513,23 +6518,23 @@
       <c r="S82" s="11"/>
       <c r="T82" s="11"/>
       <c r="U82" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V82" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W82" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X82" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y82" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z82" s="12"/>
       <c r="AA82" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.35">
@@ -6554,23 +6559,23 @@
       <c r="S83" s="11"/>
       <c r="T83" s="11"/>
       <c r="U83" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V83" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W83" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X83" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y83" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z83" s="12"/>
       <c r="AA83" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.35">
@@ -6595,23 +6600,23 @@
       <c r="S84" s="11"/>
       <c r="T84" s="11"/>
       <c r="U84" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V84" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W84" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X84" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y84" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z84" s="12"/>
       <c r="AA84" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.35">
@@ -6636,23 +6641,23 @@
       <c r="S85" s="11"/>
       <c r="T85" s="11"/>
       <c r="U85" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V85" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W85" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X85" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y85" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z85" s="12"/>
       <c r="AA85" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.35">
@@ -6677,23 +6682,23 @@
       <c r="S86" s="11"/>
       <c r="T86" s="11"/>
       <c r="U86" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V86" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W86" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X86" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y86" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z86" s="12"/>
       <c r="AA86" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.35">
@@ -6718,23 +6723,23 @@
       <c r="S87" s="11"/>
       <c r="T87" s="11"/>
       <c r="U87" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V87" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W87" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X87" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y87" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z87" s="12"/>
       <c r="AA87" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.35">
@@ -6759,23 +6764,23 @@
       <c r="S88" s="11"/>
       <c r="T88" s="11"/>
       <c r="U88" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V88" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W88" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X88" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y88" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z88" s="12"/>
       <c r="AA88" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.35">
@@ -6800,23 +6805,23 @@
       <c r="S89" s="11"/>
       <c r="T89" s="11"/>
       <c r="U89" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V89" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W89" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X89" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y89" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z89" s="12"/>
       <c r="AA89" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.35">
@@ -6841,23 +6846,23 @@
       <c r="S90" s="11"/>
       <c r="T90" s="11"/>
       <c r="U90" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V90" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W90" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X90" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y90" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z90" s="12"/>
       <c r="AA90" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.35">
@@ -6882,23 +6887,23 @@
       <c r="S91" s="11"/>
       <c r="T91" s="11"/>
       <c r="U91" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V91" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W91" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X91" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y91" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z91" s="12"/>
       <c r="AA91" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.35">
@@ -6923,23 +6928,23 @@
       <c r="S92" s="11"/>
       <c r="T92" s="11"/>
       <c r="U92" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V92" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W92" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X92" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y92" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z92" s="12"/>
       <c r="AA92" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.35">
@@ -6964,23 +6969,23 @@
       <c r="S93" s="11"/>
       <c r="T93" s="11"/>
       <c r="U93" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V93" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W93" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X93" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y93" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z93" s="12"/>
       <c r="AA93" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.35">
@@ -7005,23 +7010,23 @@
       <c r="S94" s="11"/>
       <c r="T94" s="11"/>
       <c r="U94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V94" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z94" s="12"/>
       <c r="AA94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.35">
@@ -7046,23 +7051,23 @@
       <c r="S95" s="11"/>
       <c r="T95" s="11"/>
       <c r="U95" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V95" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W95" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X95" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y95" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z95" s="12"/>
       <c r="AA95" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.35">
@@ -7087,23 +7092,23 @@
       <c r="S96" s="11"/>
       <c r="T96" s="11"/>
       <c r="U96" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V96" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W96" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X96" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y96" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z96" s="12"/>
       <c r="AA96" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.35">
@@ -7128,23 +7133,23 @@
       <c r="S97" s="11"/>
       <c r="T97" s="11"/>
       <c r="U97" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V97" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W97" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X97" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y97" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z97" s="12"/>
       <c r="AA97" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.35">
@@ -7169,23 +7174,23 @@
       <c r="S98" s="11"/>
       <c r="T98" s="11"/>
       <c r="U98" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V98" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W98" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X98" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y98" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z98" s="12"/>
       <c r="AA98" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.35">
@@ -7210,23 +7215,23 @@
       <c r="S99" s="11"/>
       <c r="T99" s="11"/>
       <c r="U99" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V99" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W99" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X99" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y99" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z99" s="12"/>
       <c r="AA99" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.35">
@@ -7251,23 +7256,23 @@
       <c r="S100" s="11"/>
       <c r="T100" s="11"/>
       <c r="U100" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V100" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W100" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X100" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y100" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z100" s="12"/>
       <c r="AA100" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.35">
@@ -7292,23 +7297,23 @@
       <c r="S101" s="11"/>
       <c r="T101" s="11"/>
       <c r="U101" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V101" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W101" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X101" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y101" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z101" s="12"/>
       <c r="AA101" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.35">
@@ -7333,23 +7338,23 @@
       <c r="S102" s="11"/>
       <c r="T102" s="11"/>
       <c r="U102" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V102" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W102" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X102" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y102" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z102" s="12"/>
       <c r="AA102" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.35">
@@ -7374,23 +7379,23 @@
       <c r="S103" s="11"/>
       <c r="T103" s="11"/>
       <c r="U103" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V103" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W103" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X103" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y103" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z103" s="12"/>
       <c r="AA103" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.35">
@@ -7415,23 +7420,23 @@
       <c r="S104" s="11"/>
       <c r="T104" s="11"/>
       <c r="U104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V104" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z104" s="12"/>
       <c r="AA104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -7502,40 +7507,40 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="B4" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="C4" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="D4" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="G4" s="26" t="s">
         <v>153</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" s="13">
         <v>50000</v>
@@ -7550,15 +7555,15 @@
         <v>100000</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B6" s="13">
         <v>50000</v>
@@ -7573,15 +7578,15 @@
         <v>80000</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B7" s="13">
         <v>20000</v>
@@ -7596,15 +7601,15 @@
         <v>35000</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B8" s="13">
         <v>8000</v>
@@ -7619,15 +7624,15 @@
         <v>12000</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" s="13">
         <v>10000</v>
@@ -7642,15 +7647,15 @@
         <v>20000</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" s="13">
         <v>5000</v>
@@ -7665,15 +7670,15 @@
         <v>10000</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B11" s="13">
         <v>10000</v>
@@ -7688,15 +7693,15 @@
         <v>15000</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B12" s="13">
         <v>100000</v>
@@ -7711,15 +7716,15 @@
         <v>200000</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B13" s="13">
         <v>25000</v>
@@ -7734,10 +7739,10 @@
         <v>50000</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -7748,7 +7753,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -7759,7 +7764,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E16" s="15">
         <v>6</v>
@@ -7776,24 +7781,24 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B19" s="7"/>
       <c r="E19" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B20" s="7"/>
       <c r="E20" s="19">
@@ -7802,46 +7807,46 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B21" s="7"/>
       <c r="E21" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="E22" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="E22" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B26" s="23">
         <f>SUM(E5:E11)</f>
@@ -7850,7 +7855,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B27" s="23">
         <f>SUM(E12:E13)</f>
@@ -7859,7 +7864,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B28" s="23">
         <f>B26*E16+B27</f>
@@ -7868,7 +7873,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B29" s="23">
         <f>E15*E16</f>
@@ -7877,7 +7882,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B30" s="23">
         <f>E20+B29</f>
@@ -7886,7 +7891,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B31" s="23">
         <f>MAX(0,B28-B30)</f>
@@ -7895,7 +7900,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B32" s="23">
         <f>MAX(0,B30-B28)</f>
@@ -7904,7 +7909,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B33" s="23">
         <f>E15-B26</f>
@@ -7913,7 +7918,7 @@
     </row>
     <row r="34" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B34" s="24" t="str">
         <f>IF(OR(E18="Not confirmed",E19="Not confirmed"),"NO – confirm accommodation and stipend first",IF(AND(OR(E18="Yes",AND(E18="No",E5&gt;0)),OR(E19="Yes",E19="No"),B30&gt;=B28),"Potentially affordable – verify all terms in writing","NO – funding / accommodation plan is insufficient"))</f>
@@ -7922,28 +7927,28 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="32" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7980,203 +7985,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="2" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-    </row>
-    <row r="2" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="B4" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="C4" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="D4" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="E4" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>153</v>
+      <c r="F4" s="26" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -8932,161 +8937,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+    </row>
+    <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="E4" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="E4" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
     </row>
     <row r="5" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="32">
+      <c r="A5" s="37">
         <f>COUNTA('Company Shortlist'!B5:B16)</f>
         <v>12</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="E5" s="32">
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="E5" s="37">
         <f>COUNTIF('Application Tracker'!F5:F104,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
     </row>
     <row r="6" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="E7" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="E7" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="32">
+      <c r="A8" s="37">
         <f>COUNTIF('Application Tracker'!G5:G104,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="E8" s="32">
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="E8" s="37">
         <f>COUNTIF('Application Tracker'!J5:J104,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
     </row>
     <row r="9" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="E10" s="35" t="s">
         <v>232</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="E10" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="32">
+      <c r="A11" s="37">
         <f>COUNTIF('Application Tracker'!K5:K104,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="E11" s="32">
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="E11" s="37">
         <f>COUNTIF('Application Tracker'!Q5:Q104,"Offer Received")</f>
         <v>0</v>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
     </row>
     <row r="12" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="E13" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="E13" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="32">
+      <c r="A14" s="37">
         <f>COUNTIF('Application Tracker'!X5:X104,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="E14" s="32">
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="E14" s="37">
         <f>COUNTIF('Application Tracker'!V5:V104,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="B17" s="36" t="s">
+      <c r="A17" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="D17" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>236</v>
+      <c r="E17" s="27" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A18)</f>
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E18">
         <f>COUNTIF('Application Tracker'!X5:X104,"Yes")</f>
@@ -9095,14 +9100,14 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B19">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A19)</f>
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E19">
         <f>COUNTIF('Application Tracker'!V5:V104,"Yes")</f>
@@ -9111,14 +9116,14 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B20">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A20)</f>
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E20">
         <f>COUNTIF('Application Tracker'!AA5:AA104,"Yes")</f>
@@ -9127,7 +9132,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B21">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A21)</f>
@@ -9136,7 +9141,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B22">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A22)</f>
@@ -9145,7 +9150,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B23">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A23)</f>
@@ -9154,7 +9159,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B24">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A24)</f>
@@ -9163,7 +9168,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B25">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A25)</f>
@@ -9172,7 +9177,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26">
         <f>COUNTIF('Application Tracker'!Q5:Q104,A26)</f>
@@ -9181,6 +9186,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E11:G11"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="E7:G7"/>
@@ -9197,8 +9204,6 @@
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="E11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
